--- a/client/excel/LangExcel/多语言表.xlsx
+++ b/client/excel/LangExcel/多语言表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11175" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ChineseSimplified" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="102">
   <si>
     <t>langId</t>
   </si>
@@ -36,130 +36,322 @@
     <t>描述</t>
   </si>
   <si>
-    <t>测试000</t>
-  </si>
-  <si>
-    <t>测试001</t>
-  </si>
-  <si>
-    <t>测试002</t>
-  </si>
-  <si>
-    <t>测试003</t>
-  </si>
-  <si>
-    <t>测试004</t>
-  </si>
-  <si>
-    <t>测试005</t>
-  </si>
-  <si>
-    <t>测试006</t>
-  </si>
-  <si>
-    <t>测试007</t>
-  </si>
-  <si>
-    <t>测试008</t>
-  </si>
-  <si>
-    <t>测试009</t>
-  </si>
-  <si>
-    <t>测试010</t>
-  </si>
-  <si>
-    <t>测试011</t>
-  </si>
-  <si>
-    <t>测试012</t>
-  </si>
-  <si>
-    <t>测试013</t>
-  </si>
-  <si>
-    <t>测试014</t>
-  </si>
-  <si>
-    <t>测试015</t>
-  </si>
-  <si>
-    <t>测试016</t>
-  </si>
-  <si>
-    <t>测试017</t>
-  </si>
-  <si>
-    <t>测试018</t>
-  </si>
-  <si>
-    <t>测试019</t>
-  </si>
-  <si>
-    <t>测试020</t>
-  </si>
-  <si>
-    <t>test000</t>
-  </si>
-  <si>
-    <t>test001</t>
-  </si>
-  <si>
-    <t>test002</t>
-  </si>
-  <si>
-    <t>test003</t>
-  </si>
-  <si>
-    <t>test004</t>
-  </si>
-  <si>
-    <t>test005</t>
-  </si>
-  <si>
-    <t>test006</t>
-  </si>
-  <si>
-    <t>test007</t>
-  </si>
-  <si>
-    <t>test008</t>
-  </si>
-  <si>
-    <t>test009</t>
-  </si>
-  <si>
-    <t>test010</t>
-  </si>
-  <si>
-    <t>test011</t>
-  </si>
-  <si>
-    <t>test012</t>
-  </si>
-  <si>
-    <t>test013</t>
-  </si>
-  <si>
-    <t>test014</t>
-  </si>
-  <si>
-    <t>test015</t>
-  </si>
-  <si>
-    <t>test016</t>
-  </si>
-  <si>
-    <t>test017</t>
-  </si>
-  <si>
-    <t>test018</t>
-  </si>
-  <si>
-    <t>test019</t>
-  </si>
-  <si>
-    <t>test020</t>
+    <t>備註1</t>
+  </si>
+  <si>
+    <t>備註2</t>
+  </si>
+  <si>
+    <t>VIP：</t>
+  </si>
+  <si>
+    <t>大廳</t>
+  </si>
+  <si>
+    <t>首充</t>
+  </si>
+  <si>
+    <t>儲錢罐</t>
+  </si>
+  <si>
+    <t>VIP專享特權</t>
+  </si>
+  <si>
+    <t>通知</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>電子</t>
+  </si>
+  <si>
+    <t>策略</t>
+  </si>
+  <si>
+    <t>喜歡</t>
+  </si>
+  <si>
+    <t>對戰</t>
+  </si>
+  <si>
+    <t>賭場</t>
+  </si>
+  <si>
+    <t>排行</t>
+  </si>
+  <si>
+    <t>任務</t>
+  </si>
+  <si>
+    <t>奪寶</t>
+  </si>
+  <si>
+    <t>基金</t>
+  </si>
+  <si>
+    <t>安全</t>
+  </si>
+  <si>
+    <t>查看更多</t>
+  </si>
+  <si>
+    <t>禮包</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>旅途</t>
+  </si>
+  <si>
+    <t>郵箱</t>
+  </si>
+  <si>
+    <t>客服</t>
+  </si>
+  <si>
+    <t>關閉</t>
+  </si>
+  <si>
+    <t>郵件</t>
+  </si>
+  <si>
+    <t>背包</t>
+  </si>
+  <si>
+    <t>登陸</t>
+  </si>
+  <si>
+    <t>收集（圖片）投資地區觸發超級列車</t>
+  </si>
+  <si>
+    <t>美元快遞</t>
+  </si>
+  <si>
+    <t>最終得獎</t>
+  </si>
+  <si>
+    <t>最終下註</t>
+  </si>
+  <si>
+    <t>明智的選擇</t>
+  </si>
+  <si>
+    <t>得獎</t>
+  </si>
+  <si>
+    <t>繼續努力</t>
+  </si>
+  <si>
+    <t>高光</t>
+  </si>
+  <si>
+    <t>賠付</t>
+  </si>
+  <si>
+    <t>免費遊戲</t>
+  </si>
+  <si>
+    <t>投資地區</t>
+  </si>
+  <si>
+    <t>支付線</t>
+  </si>
+  <si>
+    <t>當（圖片）或（圖片）出現在卷軸5上時，美元快遞功能將被觸發，並且（圖片）、 （图片）、（图片）、（图片）， 或（圖片）出現在卷軸1、2、3或4.3或更多（圖片）上，觸發選擇功能。 收藏（圖片）投資全國，大獲全勝！ （图片） 替換除（圖片）以外的所有符號， （图片）,（图片）,（图片）,（图片）,（图片）,（图片）,（图片） 以及（圖片）</t>
+  </si>
+  <si>
+    <t>3張或更多（圖片）可在免費遊戲和美元快遞功能之間進行選擇。 在免費遊戲期間， （图片） 將隨機更改為（圖片）或（圖片）並參與支付線。</t>
+  </si>
+  <si>
+    <t>（图片） 在卷軸1、2、3或4上，如果卷軸5上有（圖片），則（圖片）上的所有獎品都將獲得獎勵。
+（图片） 在卷軸1、2、3或4上，如果卷軸5上有（圖片），則會觸發美元快遞！
+每張（圖片）上的獎金是（圖片）的總價值</t>
+  </si>
+  <si>
+    <t>當（圖片）， （图片）,（图片） 或（圖片）落在卷軸1、2、3或4上，而（圖片）則落在卷軸5上，每張（圖片）， （图片）,（图片） 或（圖片）獎勵美元快遞！
+當（圖片）， （图片）,（图片） 或者（圖片）落在卷軸1、2、3或4上，（圖片）放在卷軸5上，每列火車都會獎勵一美元快遞！ 每張圖片的獎金是
+以及（圖片）， （图片）,（图片）,（图片） 以及（圖片）。</t>
+  </si>
+  <si>
+    <t>收藏（圖片）投資全國，大獲全勝！
+從東海岸到西海岸共有8個師。
+每個分區，可以選擇3個州進行投資。 當所有3個狀態
+在該部門成功投資後，它觸發了黃金列車快車。
+在所有部門都完成投資後，5號卷軸上的（圖片）會觸發Super Dollar Express。</t>
+  </si>
+  <si>
+    <t>返回遊戲</t>
+  </si>
+  <si>
+    <t>選擇一個功能</t>
+  </si>
+  <si>
+    <t>免費遊戲（圖片）&amp; （图片）</t>
+  </si>
+  <si>
+    <t>你贏了</t>
+  </si>
+  <si>
+    <t>（图片） 在美元快遞期間攜帶巨額獎品</t>
+  </si>
+  <si>
+    <t>收集（圖片）以投資地圖上的所有部門</t>
+  </si>
+  <si>
+    <t>森林人</t>
+  </si>
+  <si>
+    <t>VIP:</t>
+  </si>
+  <si>
+    <t>First charge</t>
+  </si>
+  <si>
+    <t>Piggy bank</t>
+  </si>
+  <si>
+    <t>VIP exclusive privileges</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Electronic</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>Like</t>
+  </si>
+  <si>
+    <t>Battle</t>
+  </si>
+  <si>
+    <t>Casino</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>Mission</t>
+  </si>
+  <si>
+    <t>Treasure hunt</t>
+  </si>
+  <si>
+    <t>Fund</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>View more</t>
+  </si>
+  <si>
+    <t>Gift pack</t>
+  </si>
+  <si>
+    <t>Mall</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Customer service</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Collect（图片）to invest in
+all divisions and trigger the
+SUPEREXPRESS.</t>
+  </si>
+  <si>
+    <t>TOTAL WIN</t>
+  </si>
+  <si>
+    <t>TOTAL BET</t>
+  </si>
+  <si>
+    <t>WISE CHOICE！</t>
+  </si>
+  <si>
+    <t>明智的選擇！</t>
+  </si>
+  <si>
+    <t>YOU WON</t>
+  </si>
+  <si>
+    <t>COLLECT</t>
+  </si>
+  <si>
+    <t>KEEP UP！</t>
+  </si>
+  <si>
+    <t>DOLLAR EXPRESS</t>
+  </si>
+  <si>
+    <t>HIGHLLIGHTS</t>
+  </si>
+  <si>
+    <t>PAYS</t>
+  </si>
+  <si>
+    <t>FREE GAMES</t>
+  </si>
+  <si>
+    <t>INVEST THE NATION</t>
+  </si>
+  <si>
+    <t>PAYLINES</t>
+  </si>
+  <si>
+    <t>Dollar Express Feature will be triggered when either（图片）or（图片）appears on reel 5, and（图片）、（图片）、（图片）、（图片），or（图片）appears on reels 1,2,3 or 4.3 or more（图片）trigger Choice Feature.Collect（图片）to invest in the nation and win big!（图片）substitutes for all symbols except（图片）,（图片）,（图片）,（图片）,（图片）,（图片）,（图片）,（图片）and（图片）</t>
+  </si>
+  <si>
+    <t>3 or more（图片）award a choice between Free Games and Dollar Express Feature.During Free Games,（图片）will randomly change into（图片）or （图片）and participate in payline.</t>
+  </si>
+  <si>
+    <t>（图片）on reel 1,2,3,or 4 with（图片）on reel 5 awards all prizes on the（图片）.
+（图片）on reel 1,2,3, or 4 with（图片）on reel 5 triggers Dollar Express!
+The prize on each（图片）is the total value amount on（图片）</t>
+  </si>
+  <si>
+    <t>When（图片）,（图片）,（图片）or（图片）land on reel 1,2,3,or 4 with（图片）on reel 5, every（图片）,（图片）,（图片）or（图片）awards a Dollar Express!
+When（图片）,（图片）,（图片）or（图片）land on reel 1,2,3,or 4 with（图片）on reel 5,every train awards a Dollar Express! The prize on each（图片）is the total value amount on
+and（图片）,（图片）,（图片）,（图片）and（图片）.</t>
+  </si>
+  <si>
+    <t>Collect (图片) to invest in the nation and win big!
+There are a total of 8 divisions from the East Coast to the West Coast.In
+each division, 3 states can be selected for investment.When all 3 states
+in the division are successfully invested in, it triggers a Gold Train Express.
+After all divisions have been invested in, a Super Dollar Express is triggered with（图片）on reel 5.</t>
+  </si>
+  <si>
+    <t>BACK TO GAME</t>
+  </si>
+  <si>
+    <t>CHOOSE A FEATURE</t>
+  </si>
+  <si>
+    <t>FREE GAMES WITH（图片）&amp;（图片）</t>
+  </si>
+  <si>
+    <t>（图片）CARRIES A HUGE PRIZES DURING DOLLAR EXPRESS</t>
+  </si>
+  <si>
+    <t>COLLECT（图片）TO INVEST ALL DIVISIONS ON THE MAP</t>
   </si>
 </sst>
 </file>
@@ -172,13 +364,39 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -334,6 +552,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -485,12 +709,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,139 +863,160 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="fill" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1127,187 +1366,584 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="15" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35" style="2" customWidth="1"/>
+    <col min="3" max="4" width="13.25" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2">
         <v>10001</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2">
         <v>10002</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
         <v>10003</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
         <v>10004</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2">
         <v>10005</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2">
         <v>10006</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2">
         <v>10007</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2">
         <v>10008</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2">
         <v>10009</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2">
         <v>10010</v>
       </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2">
         <v>10011</v>
       </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2">
         <v>10012</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2">
         <v>10013</v>
       </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2">
         <v>10014</v>
       </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2">
         <v>10015</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2">
         <v>10016</v>
       </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2">
         <v>10017</v>
       </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2">
         <v>10018</v>
       </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2">
         <v>10019</v>
       </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2">
         <v>10020</v>
       </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2">
         <v>10021</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2">
+        <v>10022</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2">
+        <v>10023</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2">
+        <v>11000</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2">
+        <v>12000</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="2">
+        <v>13000</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2">
+        <v>14000</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="2">
+        <v>100100001</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2">
+        <v>100100002</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="2">
+        <v>100100003</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="2">
+        <v>100100004</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="2">
+        <v>100100005</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2">
+        <v>100100006</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>100100007</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>100100008</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>100100009</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>100100010</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>100100011</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>100100012</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>100100013</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>100100014</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>100100015</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>100100016</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>100100017</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>100100018</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2">
+        <v>100100019</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2">
+        <v>100100020</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2">
+        <v>100100021</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2">
+        <v>100100022</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2">
+        <v>100100023</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2">
+        <v>100100024</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>100200001</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1320,187 +1956,726 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.125" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
         <v>10001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>10002</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>10003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>10004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>10005</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>10006</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
+        <v>10007</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
+        <v>10008</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
+        <v>10009</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
+        <v>10010</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
+        <v>10011</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
+        <v>10012</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
+        <v>10013</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
+        <v>10014</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
+        <v>10015</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
+        <v>10016</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
+        <v>10017</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
+        <v>10018</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2">
+        <v>10019</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>10002</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="2">
+        <v>10020</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>10003</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="2">
+        <v>10021</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>10004</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" s="2">
+        <v>10022</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>10005</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="2">
+        <v>10023</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>10006</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="2">
+        <v>11000</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>10007</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="2">
+        <v>12000</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>10008</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" s="2">
+        <v>13000</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2">
+        <v>14000</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>10009</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="2">
+        <v>100100001</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>10011</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="30" spans="1:4">
+      <c r="A30" s="2">
+        <v>100100002</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>10012</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="2">
+        <v>100100003</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>10013</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>10014</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="32" spans="1:4">
+      <c r="A32" s="2">
+        <v>100100004</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2">
+        <v>100100005</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>10015</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="34" spans="1:4">
+      <c r="A34" s="2">
+        <v>100100006</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2">
+        <v>100100007</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>10016</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="2">
+        <v>100100008</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2">
+        <v>100100009</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>10017</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="38" spans="1:4">
+      <c r="A38" s="2">
+        <v>100100010</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>10018</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="39" spans="1:4">
+      <c r="A39" s="2">
+        <v>100100011</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>10019</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="40" spans="1:4">
+      <c r="A40" s="2">
+        <v>100100012</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>10020</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="41" spans="1:4">
+      <c r="A41" s="2">
+        <v>100100013</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>10021</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="42" spans="1:4">
+      <c r="A42" s="2">
+        <v>100100014</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="2">
+        <v>100100015</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2">
+        <v>100100016</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="2">
+        <v>100100017</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2">
+        <v>100100018</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="2">
+        <v>100100019</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="2">
+        <v>100100020</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="2">
+        <v>100100021</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="2">
+        <v>100100022</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="2">
+        <v>100100023</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2">
+        <v>100100024</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="2">
+        <v>100200001</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/client/excel/LangExcel/多语言表.xlsx
+++ b/client/excel/LangExcel/多语言表.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="469">
   <si>
     <t>langId</t>
   </si>
@@ -200,7 +200,599 @@
     <t>收集（圖片）以投資地圖上的所有部門</t>
   </si>
   <si>
+    <t>提高賭注解鎖！</t>
+  </si>
+  <si>
     <t>森林人</t>
+  </si>
+  <si>
+    <t>分散</t>
+  </si>
+  <si>
+    <t>3（圖片）落在卷軸1、3和8上會觸發輪盤獎勵</t>
+  </si>
+  <si>
+    <t>野生的</t>
+  </si>
+  <si>
+    <t>（图片） 替代所有符號，但（圖片）和（圖片）除外</t>
+  </si>
+  <si>
+    <t>捕獲獎金</t>
+  </si>
+  <si>
+    <t>（图片） 落在沒有（圖片）的位置將在下一次旋轉中成為該位置上的鎖定（圖片）</t>
+  </si>
+  <si>
+    <t>（图片） 如果落在由（圖片）框起的位置，則（圖片）上顯示的值將複製到連接組中的所有相鄰（圖片）</t>
+  </si>
+  <si>
+    <t>這些位置將獎勵（圖片）上顯示的值，並且（圖片）將在下一次旋轉時删除</t>
+  </si>
+  <si>
+    <t>在捕獲獎金期間贏取迷你、小型獎品</t>
+  </si>
+  <si>
+    <t>自由旋轉</t>
+  </si>
+  <si>
+    <t>3（圖片）落在卷軸1、3和5上會觸發輪盤獎勵</t>
+  </si>
+  <si>
+    <t>在輪盤獎勵期間贏得免費旋轉大滿貫或大獎</t>
+  </si>
+  <si>
+    <t>在自由旋轉開始之前，一些（圖片）被授予隨機位置</t>
+  </si>
+  <si>
+    <t>基自旋中的影像不會出現在自由自旋中</t>
+  </si>
+  <si>
+    <t>超級自由旋轉</t>
+  </si>
+  <si>
+    <t>每7次免費旋轉可獲得晚餐免費旋轉</t>
+  </si>
+  <si>
+    <t>在超自由旋轉過程中，圖片可能會膨脹到周圍的位置</t>
+  </si>
+  <si>
+    <t>超級自由旋轉以平均賭注進行</t>
+  </si>
+  <si>
+    <t>付款線上的任何（图片）都將獲得付款</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>當（图片）在獲勝的薪水線上時，乘數或JACKPOT將被支付</t>
+  </si>
+  <si>
+    <t>做得好！</t>
+  </si>
+  <si>
+    <t>棒極了！</t>
+  </si>
+  <si>
+    <t>太棒了！</t>
+  </si>
+  <si>
+    <t>甜蜜的勝利！</t>
+  </si>
+  <si>
+    <t>（图片） 它是野生的，只出現在第三個卷軸上，帶有乘數或頭獎。 乘數在5到500之間。
+如果（图片）位於中獎賠付線上，則乘數將應用於總投注，並添加到總賠付中，頭獎也將被添加。</t>
+  </si>
+  <si>
+    <t>野牛財富</t>
+  </si>
+  <si>
+    <t>野牛來了</t>
+  </si>
+  <si>
+    <t>每個（圖片）獎項（圖片）最多5次。 （图片）（图片） 獎勵加倍或三倍。</t>
+  </si>
+  <si>
+    <t>車輪獎勵</t>
+  </si>
+  <si>
+    <t>收集（圖片）會觸發超級獎金。</t>
+  </si>
+  <si>
+    <t>高光區域</t>
+  </si>
+  <si>
+    <t>3、4或5（圖片）獎勵10、15或20款免費遊戲。</t>
+  </si>
+  <si>
+    <t>6張或以上（圖片）觸發野牛即將到來的豪華獎勵遊戲。</t>
+  </si>
+  <si>
+    <t>當（圖片） （图片）（图片） 出現在獎勵遊戲中。</t>
+  </si>
+  <si>
+    <t>收集（圖片）有機會在基礎遊戲中贏得超級野牛獎金。</t>
+  </si>
+  <si>
+    <t>支出</t>
+  </si>
+  <si>
+    <t>（图片）（图片）（图片） 替代所有符號，但圖片除外 （图片）（图片）（图片）（图片）（图片） 以及（圖片）。</t>
+  </si>
+  <si>
+    <t>（图片） 僅出現在卷軸2、3和4上。</t>
+  </si>
+  <si>
+    <t>此頁面上顯示的值表示在總投注100時可能獲得的獎勵。</t>
+  </si>
+  <si>
+    <t>3、4或5（圖片）在基礎遊戲期間獎勵10、15或25個免費遊戲，並在卷軸上添加更多（圖片）符號。</t>
+  </si>
+  <si>
+    <t>3、4或5（圖片）獎勵10、15或25個額外的免費遊戲。</t>
+  </si>
+  <si>
+    <t>車輪遊戲</t>
+  </si>
+  <si>
+    <t>在基礎遊戲中，收集（圖片）以填充欄來玩輪盤遊戲。</t>
+  </si>
+  <si>
+    <t>輪盤遊戲獎勵3次輪盤旋轉，以贏得硬幣獎勵或超級野牛即將到來的獎金。</t>
+  </si>
+  <si>
+    <t>野牛即將豪華上市</t>
+  </si>
+  <si>
+    <t>6張或更多圖片觸發野牛獎勵。</t>
+  </si>
+  <si>
+    <t>獎勵的初始旋轉和初始銀行價值由下錶確定：</t>
+  </si>
+  <si>
+    <t>符號數量</t>
+  </si>
+  <si>
+    <t>旋轉次數</t>
+  </si>
+  <si>
+    <t>銀行價值</t>
+  </si>
+  <si>
+    <t>總賭注</t>
+  </si>
+  <si>
+    <t>出現在卷軸上的額外（圖片）獎品將添加到銀行。</t>
+  </si>
+  <si>
+    <t>在以相同旋轉管道授予銀行價值之前，將（圖片）的獎金添加到銀行。</t>
+  </si>
+  <si>
+    <t>當（圖片）落在卷軸上時，銀行價值可能會被獎勵1到5倍。 （图片） 獎勵加倍，獎勵加倍。</t>
+  </si>
+  <si>
+    <t>（图片）  僅在獎勵遊戲期間出現在轉軸5上，並獎勵額外旋轉1次。</t>
+  </si>
+  <si>
+    <t>（图片） 和（圖片）僅在基礎遊戲和免費遊戲期間出現。</t>
+  </si>
+  <si>
+    <t>當（圖片）或（圖片）出現在卷軸上時，將授予大獎或主要頭獎。</t>
+  </si>
+  <si>
+    <t>（图片）  和（圖片）僅在獎勵遊戲期間出現。</t>
+  </si>
+  <si>
+    <t>（图片） 在野牛即將到來和超級野牛即將到來的獎金遊戲中不會出現。</t>
+  </si>
+  <si>
+    <t>超級野牛即將到來獎金</t>
+  </si>
+  <si>
+    <t>從輪盤遊戲中收集3（圖片），觸發超級野牛即將到來的獎勵遊戲。</t>
+  </si>
+  <si>
+    <t>當（圖片）落在卷軸上時，銀行價值可能會被獎勵3至15倍。</t>
+  </si>
+  <si>
+    <t>（图片）  和（圖片）僅在超級獎金遊戲期間出現。</t>
+  </si>
+  <si>
+    <t>（图片） 在超級野牛即將到來和超級野牛即將來臨的獎金遊戲中不要出現。</t>
+  </si>
+  <si>
+    <t>火線不能越過</t>
+  </si>
+  <si>
+    <t>消防车</t>
+  </si>
+  <si>
+    <t>MINI 已解鎖！</t>
+  </si>
+  <si>
+    <t>MINOR 已解鎖！</t>
+  </si>
+  <si>
+    <t>MAJOR 已解鎖！</t>
+  </si>
+  <si>
+    <t>GRAND 已解鎖！</t>
+  </si>
+  <si>
+    <t>亮點</t>
+  </si>
+  <si>
+    <t>消防車獎金</t>
+  </si>
+  <si>
+    <t>支付</t>
+  </si>
+  <si>
+    <t>免費旋轉</t>
+  </si>
+  <si>
+    <t>消防車財富</t>
+  </si>
+  <si>
+    <t>頭獎</t>
+  </si>
+  <si>
+    <t>通過在支付線上獲勝來清除所有明火，以觸發免費遊戲。
+6張或更多（圖片）會觸發消防車RICHES。
+收集（圖片）也會觸發消防車RICHES。 如果觸發，它將填充（圖片）到6
+並隨機獎勵（圖片）， （图片）,（图片） 或（圖片）。</t>
+  </si>
+  <si>
+    <t>（图片） 觸發消防車獎金：可授予GRAND,MAJOR,MINOR,MINI和硬幣獎金。</t>
+  </si>
+  <si>
+    <t>（图片） 是WILD，可替代除（圖片）以外的所有符號</t>
+  </si>
+  <si>
+    <t>此頁面上顯示的值表示下注100時的獎勵。</t>
+  </si>
+  <si>
+    <t>通過在支付線上獲勝來清除所有（圖片），以觸發免費遊戲。
+獲得8次免費旋轉。
+第三卷僅包含（圖片）,（圖片）和（圖片）.
+（图片),（图片),（图片) 可能以x2、x3或x5的隨機倍數出現。
+每張(圖片)獎勵1次額外旋轉。</t>
+  </si>
+  <si>
+    <t>6張或更多（圖片）會觸發消防車RICHES。
+收集（圖片）也會觸發消防車RICHES。 如果觸發，它將填充（圖片）到6
+並隨機獎勵（圖片）， （图片）,（图片） 或（圖片）。
+（图片） 是神秘的象徵，它可以轉化為（圖片）， （图片）,（图片） 或（圖片）。
+當（圖片）落在未鎖定的行上時，另一行將被解鎖。
+當所有行被解鎖時，（图片）著陸解鎖卷軸組上方的圖片。
+（图片） 在消防車獎勵結束時觸發消防車財富。</t>
+  </si>
+  <si>
+    <t>（图片） 收集卷軸上的所有圖片，然後轉換為具有組合值的新圖片。
+（图片） 觸發迷你遊戲並立即播放。
+（图片） 將硬幣獎勵值添加到隨機（圖片）並鎖定到位，它將在所有剩餘的旋轉中重複。
+（图片） 為卷軸上的所有圖片添加硬幣獎勵值，然後消失。</t>
+  </si>
+  <si>
+    <t>開鎖
+贏得GRAND：累積獎金遞增
+贏得MAJOR：累積獎金遞增
+贏得MINOR：累積獎金遞增
+贏得MINI：累積獎金遞增</t>
+  </si>
+  <si>
+    <t>鎖定
+贏得GRAND：總賭注的100倍
+贏得MAJOR：總賭注的50倍
+贏得MINOR：總賭注的20倍
+贏得MINI：總賭注的10倍</t>
+  </si>
+  <si>
+    <t>再來一張（圖片）觸發消防車獎金</t>
+  </si>
+  <si>
+    <t>消防車獎勵在功能後開始</t>
+  </si>
+  <si>
+    <t>紅方勝</t>
+  </si>
+  <si>
+    <t>红黑大战</t>
+  </si>
+  <si>
+    <t>黑方勝</t>
+  </si>
+  <si>
+    <t>正在結算</t>
+  </si>
+  <si>
+    <t>紅方</t>
+  </si>
+  <si>
+    <t>黑方</t>
+  </si>
+  <si>
+    <t>幸運一擊</t>
+  </si>
+  <si>
+    <t>豹子10倍</t>
+  </si>
+  <si>
+    <t>順金5倍</t>
+  </si>
+  <si>
+    <t>金花3倍</t>
+  </si>
+  <si>
+    <t>順子2倍</t>
+  </si>
+  <si>
+    <t>對子9-A 1倍</t>
+  </si>
+  <si>
+    <t>單張</t>
+  </si>
+  <si>
+    <t>對子</t>
+  </si>
+  <si>
+    <t>順子</t>
+  </si>
+  <si>
+    <t>金花</t>
+  </si>
+  <si>
+    <t>順金</t>
+  </si>
+  <si>
+    <t>豹子</t>
+  </si>
+  <si>
+    <t>開始下注</t>
+  </si>
+  <si>
+    <t>請下注</t>
+  </si>
+  <si>
+    <t>續押</t>
+  </si>
+  <si>
+    <t>局數</t>
+  </si>
+  <si>
+    <t>紅方趨勢</t>
+  </si>
+  <si>
+    <t>黑方趨勢</t>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>幫助</t>
+  </si>
+  <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>充值</t>
+  </si>
+  <si>
+    <t>充值記錄</t>
+  </si>
+  <si>
+    <t>規則</t>
+  </si>
+  <si>
+    <t>遊戲規則</t>
+  </si>
+  <si>
+    <t>根據牌型大小判斷勝負，若牌型相同則雙方從大到小依次比較數位的大
+小，若雙方三張牌數位相同，則比較最大牌的花色。
+特別聲明：炸金花中的JQK&lt;A23，以及雜花235&gt;豹子在本遊戲中不生效
+遊戲使用一副去除大小王的撲克牌，共4個花色52張牌</t>
+  </si>
+  <si>
+    <t>1.豹子：三張數位相同的牌（AAA最大，222最小）
+2.順金：花色相同並且三張數位連續的牌（AKQ最大，A23最小）
+3.金花：花色相同但是三張數位不連續的牌（AKJ最大，532最小）
+4.順子：三張連續數位的牌（AKQ最大，A23最小）
+5.對子：三張中只有兩張數位一樣的牌（AAK最大，223最小）
+6.散牌：三張不相同的牌（AKJ最大，532最小）</t>
+  </si>
+  <si>
+    <t>牌型：豹子&gt;順金&gt;金花&gt;順子&gt;對子&gt;散牌
+點數：A&gt;K&gt;Q&gt;J&gt;10&gt;9&gt;8&gt;7&gt;6&gt;5&gt;4&gt;3&gt;2
+花色：黑桃&gt;紅桃&gt;櫻花&gt;方塊</t>
+  </si>
+  <si>
+    <t>投注區域</t>
+  </si>
+  <si>
+    <t>紅方：紅方勝利獲得相應倍率X1
+黑方：黑方勝利獲得相應倍率X1
+幸運一擊：勝利方牌型為特殊牌型，可獲得相應倍率。</t>
+  </si>
+  <si>
+    <t>牌型    倍率
+豹子    10倍
+順金    5倍
+金花    3倍
+順子    2倍
+對子9-A 1倍</t>
+  </si>
+  <si>
+    <t>注：收取贏家3%稅費</t>
+  </si>
+  <si>
+    <t>和</t>
+  </si>
+  <si>
+    <t>龙虎斗</t>
+  </si>
+  <si>
+    <t>龍贏</t>
+  </si>
+  <si>
+    <t>虎贏</t>
+  </si>
+  <si>
+    <t>等待開局</t>
+  </si>
+  <si>
+    <t>龍</t>
+  </si>
+  <si>
+    <t>虎</t>
+  </si>
+  <si>
+    <t>下注階段即將結束</t>
+  </si>
+  <si>
+    <t>下注結束</t>
+  </si>
+  <si>
+    <t>一賠一</t>
+  </si>
+  <si>
+    <t>一賠八</t>
+  </si>
+  <si>
+    <t>龍趨勢</t>
+  </si>
+  <si>
+    <t>虎趨勢</t>
+  </si>
+  <si>
+    <t>1.龍虎鬥是種簡單休閒的娛樂遊戲，牌面大小不比花色，只比點數。
+2.點數大小由K到A，K為最大點數，A為最小點數，相同點數為和。
+(K&gt;Q&gt;J&gt;10&gt;9&gt;8&gt;7&gt;6&gt;5&gt;4&gt;3&gt;2&gt;A)
+3.發牌前預測龍虎大小，可押注“龍”、“虎”、“和”三個區域。
+4.開牌時荷官先發一張牌至龍區域，再發一張牌至虎區域，對比牌麵點
+數大者獲勝。</t>
+  </si>
+  <si>
+    <t>1.龍：1賠1（和局全退）
+2.虎：1賠1（和局全退）
+3.和：1賠8</t>
+  </si>
+  <si>
+    <t>飞禽走兽</t>
+  </si>
+  <si>
+    <t>如何玩</t>
+  </si>
+  <si>
+    <t>鳥類和動物共有12個投資領域，每個領域都有不同的獲勝倍數。 獲勝後，他們將獲得與倍數相對應的獎勵</t>
+  </si>
+  <si>
+    <t>鳥類：圖片6倍，圖片8倍，圖片8x，圖片12x，鳥類總投資面積2x</t>
+  </si>
+  <si>
+    <t>野獸：影像6x，影像8x，影像8 x，影像12x，野獸總投影面積2x</t>
+  </si>
+  <si>
+    <t>鯊魚：圖片24次，圖片100次</t>
+  </si>
+  <si>
+    <t>其他：在圖片中所有投資獲勝的玩家將根據相應的倍數獲得獎勵</t>
+  </si>
+  <si>
+    <t>圖片中的所有玩家輸入都失敗了</t>
+  </si>
+  <si>
+    <t>進入遊戲後，玩家可以選擇投資不同金額的硬幣</t>
+  </si>
+  <si>
+    <t>無法參加抽獎，請等待下一輪開始</t>
+  </si>
+  <si>
+    <t>奔驰宝马</t>
+  </si>
+  <si>
+    <t>設置</t>
+  </si>
+  <si>
+    <t>續投</t>
+  </si>
+  <si>
+    <t>開始下註</t>
+  </si>
+  <si>
+    <t>下註結束</t>
+  </si>
+  <si>
+    <t>下註時間已過</t>
+  </si>
+  <si>
+    <t>請下註</t>
+  </si>
+  <si>
+    <t>百家樂</t>
+  </si>
+  <si>
+    <t>攤牌剩餘</t>
+  </si>
+  <si>
+    <t>結算中</t>
+  </si>
+  <si>
+    <t>下注中</t>
+  </si>
+  <si>
+    <t>莊問路</t>
+  </si>
+  <si>
+    <t>閑問路</t>
+  </si>
+  <si>
+    <t>進入遊戲</t>
+  </si>
+  <si>
+    <t>莊</t>
+  </si>
+  <si>
+    <t>閑</t>
+  </si>
+  <si>
+    <t>莊對子</t>
+  </si>
+  <si>
+    <t>閑對子</t>
+  </si>
+  <si>
+    <t>點</t>
+  </si>
+  <si>
+    <t>下注</t>
+  </si>
+  <si>
+    <t>局</t>
+  </si>
+  <si>
+    <t>獲勝</t>
+  </si>
+  <si>
+    <t>音樂</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>設置音樂</t>
+  </si>
+  <si>
+    <t>正在加載...請稍後...</t>
+  </si>
+  <si>
+    <t>您已經好久未進行投注了，去其他遊戲試試手氣吧</t>
+  </si>
+  <si>
+    <t>確定</t>
+  </si>
+  <si>
+    <t>您已押注，無法退出遊戲！</t>
   </si>
   <si>
     <t>VIP:</t>
@@ -352,6 +944,612 @@
   </si>
   <si>
     <t>COLLECT（图片）TO INVEST ALL DIVISIONS ON THE MAP</t>
+  </si>
+  <si>
+    <t>RAISE BET TO UNLOCK!</t>
+  </si>
+  <si>
+    <t>forestman</t>
+  </si>
+  <si>
+    <t>Scatter</t>
+  </si>
+  <si>
+    <t>3（图片）lands on reels 1,3 and 8 trigger the Wheel Bonus</t>
+  </si>
+  <si>
+    <t>wild</t>
+  </si>
+  <si>
+    <t>（图片）substitutes for all symbols except （图片）and （图片）</t>
+  </si>
+  <si>
+    <t>Catch bonus</t>
+  </si>
+  <si>
+    <t>（图片）lands on a position without（图片）will become a locked （图片）over that position in the next spin</t>
+  </si>
+  <si>
+    <t>（图片）lands on a position framed by （图片）, the values displayed on the （图片）will duplicate to all the adjacent （图片）in the connected group</t>
+  </si>
+  <si>
+    <t>Those positions will award the values displayed on （图片）and （图片） will be removed on the next spin</t>
+  </si>
+  <si>
+    <t>Win prizes ,mini, minor, during the catch bonus</t>
+  </si>
+  <si>
+    <t>Free spin</t>
+  </si>
+  <si>
+    <t>3 （图片） lands on reels 1,3 and 5 trigger the wheel bonus</t>
+  </si>
+  <si>
+    <t>win free spin major or grand during the wheel bonus</t>
+  </si>
+  <si>
+    <t>before free spin started, a number of （图片） are awarded to random positions</t>
+  </si>
+  <si>
+    <t>the （图片） in base spin do not appear in the free spin</t>
+  </si>
+  <si>
+    <t>Super free spin</t>
+  </si>
+  <si>
+    <t>supper free spin is awarded for every 7th of free spin</t>
+  </si>
+  <si>
+    <t>uring the super free spin （图片） may expand to the position around</t>
+  </si>
+  <si>
+    <t>super free spin is played at average bet</t>
+  </si>
+  <si>
+    <t>ANY（图片）ON A PAYLINE WILL AWARD A PAYOUT</t>
+  </si>
+  <si>
+    <t>THE MULTIPLIER OR JACKPOT WILL BEAWARDED WHEN（图片）IS ON THE WINNING PAYLINE</t>
+  </si>
+  <si>
+    <t>WELL DONE！</t>
+  </si>
+  <si>
+    <t>GREAT！</t>
+  </si>
+  <si>
+    <t>OUTSTANDING!</t>
+  </si>
+  <si>
+    <t>SWEET WIN!</t>
+  </si>
+  <si>
+    <t>（图片）is wild, and only appears on the 3rd reel with a multiplier or Jackpot. The multiplier ranges from 5 to 500.
+if（图片）is on a winning payline, the multiplier will be applied to thetotal bet, added to the total payout, and the jackpot will also be added.</t>
+  </si>
+  <si>
+    <t>HIGH LIGHTS</t>
+  </si>
+  <si>
+    <t>Bison Riches</t>
+  </si>
+  <si>
+    <t>野牛财富</t>
+  </si>
+  <si>
+    <t>BISON COMING</t>
+  </si>
+  <si>
+    <t>Each （图片） awards （图片） up to 5 times.（图片）（图片）double or triple the reward.</t>
+  </si>
+  <si>
+    <t>Wheel bonus</t>
+  </si>
+  <si>
+    <t>Collecting（图片）triggers super bonus.</t>
+  </si>
+  <si>
+    <t>Highlights</t>
+  </si>
+  <si>
+    <t>3,4or5（图片）award 10,15or20free games.</t>
+  </si>
+  <si>
+    <t>6 or more （图片）trigger bison coming deluxe bonus game.</t>
+  </si>
+  <si>
+    <t>The current （图标）bank value may be awarded up to 5 times when （图片）（图片）（图片）appears in bonus game.</t>
+  </si>
+  <si>
+    <t>Collect （图片）for a chance to win super bison coming bonus during base game.</t>
+  </si>
+  <si>
+    <t>Payouts</t>
+  </si>
+  <si>
+    <t>（图片）（图片）（图片）substitutes for all symbols except （图片）（图片）（图片）（图片）（图片）（图片）and（图片）.</t>
+  </si>
+  <si>
+    <t>（图片）appears on reels 2,3  and4 only.</t>
+  </si>
+  <si>
+    <t>Values displayed on this page represent the awards that may be awarded at the total bet 100.</t>
+  </si>
+  <si>
+    <t>Free games</t>
+  </si>
+  <si>
+    <t>3,4 or5 （图片） award 10,15 or 25 free games during base game with more （图片） symbols added to the reels.</t>
+  </si>
+  <si>
+    <t>3,4 or 5（图片） award 10,15 or25 extra free games.</t>
+  </si>
+  <si>
+    <t>Wheel games</t>
+  </si>
+  <si>
+    <t>During the base game， collect （图片） to fill the bar to play the wheel game.</t>
+  </si>
+  <si>
+    <t>The wheel game awards 3 wheel spins to win a coin prize or the super bison coming bonus.</t>
+  </si>
+  <si>
+    <t>Bison coming deluxe</t>
+  </si>
+  <si>
+    <t>6 or more （图片） trigger bison coming bonus.</t>
+  </si>
+  <si>
+    <t>The initial spins awarded and initial bank value is determined by the table below：</t>
+  </si>
+  <si>
+    <t>Number of symbols</t>
+  </si>
+  <si>
+    <t>number of spins</t>
+  </si>
+  <si>
+    <t>bank value</t>
+  </si>
+  <si>
+    <t>total bet</t>
+  </si>
+  <si>
+    <t>Additional （图片） prizes appearing on the reels are added to the bank.</t>
+  </si>
+  <si>
+    <t>The prizes of （图片） are added to the bank before the bank value is awarded on the same spin.</t>
+  </si>
+  <si>
+    <t>Bank value may be awarded 1 to 5 times when （图片） lands on the reels.（图片）double the reward， and （图片） triples the reward.</t>
+  </si>
+  <si>
+    <t>（图片） only appears on reels 5 during the bonus game and awards 1 additional spin.</t>
+  </si>
+  <si>
+    <t>（图片）and（图片）only appear during base games and free game.</t>
+  </si>
+  <si>
+    <t>Grand or major jackpot is awarded when （图片） or （图片）appears on the reels.</t>
+  </si>
+  <si>
+    <t>（图片） and （图片） only appear during the bonus game.</t>
+  </si>
+  <si>
+    <t>（图片）does not appear during the bison coming and super bison coming bonus game.</t>
+  </si>
+  <si>
+    <t>Super bison coming bonus</t>
+  </si>
+  <si>
+    <t>Collect 3 （图片） from wheel game to trigger the super bison coming bonus game.</t>
+  </si>
+  <si>
+    <t>Bank value may be awarded 3 to 15 times when （图片） lands on the reels.</t>
+  </si>
+  <si>
+    <t>（图片） and （图片）only appear during the super bonus game.</t>
+  </si>
+  <si>
+    <t>（图片）dose not appear during the super bison coming and super bison coming bonus game.</t>
+  </si>
+  <si>
+    <t>FIRE LINE DO NOT CROSS</t>
+  </si>
+  <si>
+    <t>MINI IS UNLOCKED！</t>
+  </si>
+  <si>
+    <t>MINOR IS UNLOCKED！</t>
+  </si>
+  <si>
+    <t>MAJOR IS UNLOCKED！</t>
+  </si>
+  <si>
+    <t>GRAND IS UNLOCKED！</t>
+  </si>
+  <si>
+    <t>HIGHLIGHTS</t>
+  </si>
+  <si>
+    <t>FIRE TRUCK BONUS</t>
+  </si>
+  <si>
+    <t>FREE SPINS</t>
+  </si>
+  <si>
+    <t>FIRE TRUCK RICHES</t>
+  </si>
+  <si>
+    <t>JACKPOTS</t>
+  </si>
+  <si>
+    <t>Clear all（图片）by winning on paylines to trigger FREE GAMES.
+6 or more（图片）triggers FIRE TRUCK RICHES.
+Collecting（图片）also triggers FIRE TRUCK RICHES.If triggered, it will fill up（图片）to 6
+and randomly award（图片）,（图片）,（图片）or（图片）.</t>
+  </si>
+  <si>
+    <t>（图片）triggers FIRE TRUCK BONUS:GRAND,MAJOR,MINOR,MINI,and coin prize value may be awarded.</t>
+  </si>
+  <si>
+    <t>（图片）is WILD and substitutes for all symbols except（图片）</t>
+  </si>
+  <si>
+    <t>Values displayed on this page represent the awards at the bet of 100.</t>
+  </si>
+  <si>
+    <t>Clear all（图片）by winning on paylines to trigger FREE GAMES.
+8 Free Spins are awarded.
+The 3rd reel contains（图片）,（图片）,and（图片）only.
+（图片),（图片),（图片)may appear with a random multiplier of x2,x3,or x5.
+Each（图片）awards 1 additional spin.</t>
+  </si>
+  <si>
+    <t>6 or more（图片）triggers FIRE TRUCK RICHES.
+Collecting（图片）also triggers FIRE TRUCK RICHES.If triggered, it will fill up（图片）to 6
+and randomly award（图片）,（图片）,（图片）or（图片）.
+（图片）is mystery symbol, it can transform into（图片）,（图片）,（图片）or（图片）.
+When（图片）lands on unlocked rows,1 additional row will be unlocked.
+When all rows are unlocked,（图片）landing unlocks（图片）above the reel set.
+（图片）triggers the FIRE TRUCK BONUS at the end of the FIRE TRUCK RICHES.</t>
+  </si>
+  <si>
+    <t>（图片）collects all（图片）on reels and then transform into a new（图片）with the combined value.
+（图片）triggers the MINI GAME and plays immediately.
+（图片）adds a coin prize value to random（图片）and locks in place, it will repeat for all remaining spins.
+（图片）adds a coin prize value to all（图片）on reels and then disappears.</t>
+  </si>
+  <si>
+    <t>UNLOCKED
+WIN GRAND：JACKPOT PROGRESSIVE
+WIN MAJOR：JACKPOT PROGRESSIVE
+WIN MINOR：JACKPOT PROGRESSIVE
+WIN MINI：JACKPOT PROGRESSIVE</t>
+  </si>
+  <si>
+    <t>LOCKED
+WIN GRAND:100X TOTAL BET
+WIN MAJOR:50X TOTAL BET
+WIN MINOR:20X TOTAL BET
+WIN MINI:10X TOTAL BET</t>
+  </si>
+  <si>
+    <t>ONE MORE（图片）TO TRIGGER FIRE TRUCK BONUS</t>
+  </si>
+  <si>
+    <t>FIRE TRUCK BONUS STARTS AFTER FEATURE</t>
+  </si>
+  <si>
+    <t>Red Win</t>
+  </si>
+  <si>
+    <t>Black Win</t>
+  </si>
+  <si>
+    <t>Settlement in progress</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Lucky</t>
+  </si>
+  <si>
+    <t>Set 10x</t>
+  </si>
+  <si>
+    <t>pure sequence 5x</t>
+  </si>
+  <si>
+    <t>Colour 3x</t>
+  </si>
+  <si>
+    <t>sequence 2x</t>
+  </si>
+  <si>
+    <t>Pair9-A 1x</t>
+  </si>
+  <si>
+    <t>High Card</t>
+  </si>
+  <si>
+    <t>Pair</t>
+  </si>
+  <si>
+    <t>sequence</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>pure sequence</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Start betting</t>
+  </si>
+  <si>
+    <t>Please place a bet</t>
+  </si>
+  <si>
+    <t>Continued betting</t>
+  </si>
+  <si>
+    <t>number of games</t>
+  </si>
+  <si>
+    <t>Red Trends</t>
+  </si>
+  <si>
+    <t>Black Trends</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Help</t>
+  </si>
+  <si>
+    <t>exit</t>
+  </si>
+  <si>
+    <t>Recharge</t>
+  </si>
+  <si>
+    <t>Recharge Record</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Game Rules</t>
+  </si>
+  <si>
+    <t>Judging the winner based on the size of the card type, if the card types are the same, both sides will compare the larger numbers in descending order
+If the numbers of the three cards on both sides are the same, compare the suit of the biggest card.
+Special Notice: JQK&lt;A23 in the Golden Flower and the Leopard in the Miscellaneous Flower 235&gt;are not effective in this game
+The game uses a deck of playing cards with 4 suits and 52 cards to remove the size king</t>
+  </si>
+  <si>
+    <t>1. Set: Three cards with the same number (AAA maximum, 222 minimum)
+2. pure sequence: A card with the same suit and three consecutive numbers (AKQ maximum, A23 minimum)
+3. Colour: A card with the same suit but three numbers that are not consecutive (AKJ is the largest, 532 is the smallest)
+4. sequence: Three consecutive number cards (AKQ maximum, A23 minimum)
+5. Pair: Only two of the three cards have the same number (AAK maximum, 223 minimum)
+6. High Card: Three different cards (AKJ maximum, 532 minimum)</t>
+  </si>
+  <si>
+    <t>Card type: Set&gt;pure sequence&gt;Colour&gt;sequence&gt;Pair&gt;High Card
+Points: A&gt;K&gt;Q&gt;J&gt;10&gt;9&gt;8&gt;7&gt;6&gt;5&gt;4&gt;3&gt;2
+Colors: Spades&gt;Hearts&gt;Cherry Blossoms&gt;Cubes</t>
+  </si>
+  <si>
+    <t>Betting area</t>
+  </si>
+  <si>
+    <t>Red: Red team wins and gains corresponding multiplier X1
+Black: Black side wins and gains corresponding multiplier X1
+Lucky: The winning card type is a special card type that can obtain the corresponding multiplier</t>
+  </si>
+  <si>
+    <t>Card type      Magnification
+Set            10x
+pure sequence  5x
+Colour         3x
+sequence       2x
+Pair           1x</t>
+  </si>
+  <si>
+    <t>Tips: 3% tax will be charged to the winner</t>
+  </si>
+  <si>
+    <t>Tie</t>
+  </si>
+  <si>
+    <t>Dragon Win</t>
+  </si>
+  <si>
+    <t>Tiger Win</t>
+  </si>
+  <si>
+    <t>Waiting for the start</t>
+  </si>
+  <si>
+    <t>Dragon</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>The betting phase is about to end</t>
+  </si>
+  <si>
+    <t>End of betting</t>
+  </si>
+  <si>
+    <t>One for one</t>
+  </si>
+  <si>
+    <t>One for eight</t>
+  </si>
+  <si>
+    <t>Dragon Trends</t>
+  </si>
+  <si>
+    <t>Tiger Trends</t>
+  </si>
+  <si>
+    <t>1. Dragon and Tiger Fight is a simple and casual entertainment game, where the size of the cards is not determined by the suit, but only by the number of points.
+2. The number of points ranges from K to A, where K is the maximum number of points, A is the minimum number of points, and the same number of points is the sum.
+(K&gt;Q&gt;J&gt;10&gt;9&gt;8&gt;7&gt;6&gt;5&gt;4&gt;3&gt;2&gt;A)
+3. Predict the size of the dragon and tiger before issuing cards, and bet on three areas: "dragon", "tiger", and "tie".
+4. When opening a card, the dealer first sends one card to the Dragon area and then another card to the Tiger area, comparin</t>
+  </si>
+  <si>
+    <t>1. Dragon: 1 for 1 (Tie will be refunded)
+2. Tiger: 1 for 1 (Tie will be refunded)
+3. And: 1 to 8 compensation</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>帮助</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Rollover</t>
+  </si>
+  <si>
+    <t>续投</t>
+  </si>
+  <si>
+    <t>Place your bets</t>
+  </si>
+  <si>
+    <t>开始下注</t>
+  </si>
+  <si>
+    <t>Betting ends</t>
+  </si>
+  <si>
+    <t>下注结束</t>
+  </si>
+  <si>
+    <t>Betting time has expired.</t>
+  </si>
+  <si>
+    <t>下注时间已过</t>
+  </si>
+  <si>
+    <t>请下注</t>
+  </si>
+  <si>
+    <t>zoo roulette</t>
+  </si>
+  <si>
+    <t>how to play</t>
+  </si>
+  <si>
+    <t>There are a total of 12 areas for birds and animals to invest in, and each area has a different winning multiple. After winning, they will receive rewards corresponding to the multiple</t>
+  </si>
+  <si>
+    <t>Birds: Image 6x, Image 8x, Image 8x, Image 12x, Total investment area of birds 2x</t>
+  </si>
+  <si>
+    <t>Beasts: Image 6x, Image 8x, Image 8x, Image 12x, Beast Total Projection Area 2x</t>
+  </si>
+  <si>
+    <t>Shark: Image 24 times, Image 100 times</t>
+  </si>
+  <si>
+    <t>Other: Players who win with all their investments in the picture will receive rewards according to corresponding multiples</t>
+  </si>
+  <si>
+    <t>All player inputs in the picture have failed</t>
+  </si>
+  <si>
+    <t>After entering the game, players can choose to invest coins of different amounts</t>
+  </si>
+  <si>
+    <t>Unable to participate in the draw, please wait for the next round to begin</t>
+  </si>
+  <si>
+    <t>Repeat</t>
+  </si>
+  <si>
+    <t>百家乐</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>Settling</t>
+  </si>
+  <si>
+    <t>Betting</t>
+  </si>
+  <si>
+    <t>Banker Predict</t>
+  </si>
+  <si>
+    <t>Player Predict</t>
+  </si>
+  <si>
+    <t>Enter the game</t>
+  </si>
+  <si>
+    <t>Banker</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>P Pair</t>
+  </si>
+  <si>
+    <t>B Pair</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Rounds</t>
+  </si>
+  <si>
+    <t>Bet</t>
+  </si>
+  <si>
+    <t>Win</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>Sound</t>
+  </si>
+  <si>
+    <t>Setting Music</t>
+  </si>
+  <si>
+    <t>Loading...Please wait...</t>
+  </si>
+  <si>
+    <t>You haven't placed a bet for a long time, try your luck in other games.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>You have placed your bet and cannot exit the game!</t>
   </si>
 </sst>
 </file>
@@ -364,7 +1562,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,6 +1593,21 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="微软雅黑 Light"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑 Light"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -863,137 +2076,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,20 +2216,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="fill" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="fill" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1077,6 +2320,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1366,26 +2616,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35" style="2" customWidth="1"/>
-    <col min="3" max="4" width="13.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="35" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="4" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1393,10 +2644,10 @@
       <c r="A2" s="2">
         <v>10001</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1404,10 +2655,10 @@
       <c r="A3" s="2">
         <v>10002</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1415,10 +2666,10 @@
       <c r="A4" s="2">
         <v>10003</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1426,10 +2677,10 @@
       <c r="A5" s="2">
         <v>10004</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1437,10 +2688,10 @@
       <c r="A6" s="2">
         <v>10005</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1448,10 +2699,10 @@
       <c r="A7" s="2">
         <v>10006</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1459,10 +2710,10 @@
       <c r="A8" s="2">
         <v>10007</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1470,10 +2721,10 @@
       <c r="A9" s="2">
         <v>10008</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1481,10 +2732,10 @@
       <c r="A10" s="2">
         <v>10009</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1492,10 +2743,10 @@
       <c r="A11" s="2">
         <v>10010</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1503,10 +2754,10 @@
       <c r="A12" s="2">
         <v>10011</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1514,10 +2765,10 @@
       <c r="A13" s="2">
         <v>10012</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1525,10 +2776,10 @@
       <c r="A14" s="2">
         <v>10013</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1536,10 +2787,10 @@
       <c r="A15" s="2">
         <v>10014</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1547,10 +2798,10 @@
       <c r="A16" s="2">
         <v>10015</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1558,10 +2809,10 @@
       <c r="A17" s="2">
         <v>10016</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1569,10 +2820,10 @@
       <c r="A18" s="2">
         <v>10017</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1580,10 +2831,10 @@
       <c r="A19" s="2">
         <v>10018</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1591,10 +2842,10 @@
       <c r="A20" s="2">
         <v>10019</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1602,10 +2853,10 @@
       <c r="A21" s="2">
         <v>10020</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1613,10 +2864,10 @@
       <c r="A22" s="2">
         <v>10021</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1624,10 +2875,10 @@
       <c r="A23" s="2">
         <v>10022</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1635,10 +2886,10 @@
       <c r="A24" s="2">
         <v>10023</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1646,7 +2897,7 @@
       <c r="A25" s="2">
         <v>11000</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1654,7 +2905,7 @@
       <c r="A26" s="2">
         <v>12000</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1662,7 +2913,7 @@
       <c r="A27" s="2">
         <v>13000</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1670,7 +2921,7 @@
       <c r="A28" s="2">
         <v>14000</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1678,10 +2929,10 @@
       <c r="A29" s="2">
         <v>100100001</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1689,10 +2940,10 @@
       <c r="A30" s="2">
         <v>100100002</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1700,10 +2951,10 @@
       <c r="A31" s="2">
         <v>100100003</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1711,10 +2962,10 @@
       <c r="A32" s="2">
         <v>100100004</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1722,10 +2973,10 @@
       <c r="A33" s="2">
         <v>100100005</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1733,10 +2984,10 @@
       <c r="A34" s="2">
         <v>100100006</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1744,10 +2995,10 @@
       <c r="A35" s="2">
         <v>100100007</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1755,10 +3006,10 @@
       <c r="A36" s="2">
         <v>100100008</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1766,10 +3017,10 @@
       <c r="A37" s="2">
         <v>100100009</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1777,10 +3028,10 @@
       <c r="A38" s="2">
         <v>100100010</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1788,10 +3039,10 @@
       <c r="A39" s="2">
         <v>100100011</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1799,10 +3050,10 @@
       <c r="A40" s="2">
         <v>100100012</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1810,10 +3061,10 @@
       <c r="A41" s="2">
         <v>100100013</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1821,10 +3072,10 @@
       <c r="A42" s="2">
         <v>100100014</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1832,10 +3083,10 @@
       <c r="A43" s="2">
         <v>100100015</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1843,10 +3094,10 @@
       <c r="A44" s="2">
         <v>100100016</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1854,10 +3105,10 @@
       <c r="A45" s="2">
         <v>100100017</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1865,10 +3116,10 @@
       <c r="A46" s="2">
         <v>100100018</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1876,10 +3127,10 @@
       <c r="A47" s="2">
         <v>100100019</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1887,10 +3138,10 @@
       <c r="A48" s="2">
         <v>100100020</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1898,10 +3149,10 @@
       <c r="A49" s="2">
         <v>100100021</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1909,10 +3160,10 @@
       <c r="A50" s="2">
         <v>100100022</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1920,10 +3171,10 @@
       <c r="A51" s="2">
         <v>100100023</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1931,19 +3182,2250 @@
       <c r="A52" s="2">
         <v>100100024</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
+        <v>100100025</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2">
         <v>100200001</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>54</v>
+      <c r="B54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" ht="17.25" spans="1:3">
+      <c r="A55" s="2">
+        <v>100200002</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" ht="17.25" spans="1:3">
+      <c r="A56" s="2">
+        <v>100200003</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" ht="17.25" spans="1:3">
+      <c r="A57" s="2">
+        <v>100200004</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" ht="17.25" spans="1:3">
+      <c r="A58" s="2">
+        <v>100200005</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" spans="1:3">
+      <c r="A59" s="2">
+        <v>100200006</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" spans="1:3">
+      <c r="A60" s="2">
+        <v>100200007</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" spans="1:3">
+      <c r="A61" s="2">
+        <v>100200008</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" ht="17.25" spans="1:3">
+      <c r="A62" s="2">
+        <v>100200009</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" ht="17.25" spans="1:3">
+      <c r="A63" s="2">
+        <v>100200010</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" spans="1:3">
+      <c r="A64" s="2">
+        <v>100200011</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" ht="17.25" spans="1:3">
+      <c r="A65" s="2">
+        <v>100200012</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" ht="17.25" spans="1:3">
+      <c r="A66" s="2">
+        <v>100200013</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" ht="17.25" spans="1:3">
+      <c r="A67" s="2">
+        <v>100200014</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" ht="17.25" spans="1:3">
+      <c r="A68" s="2">
+        <v>100200015</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" ht="17.25" spans="1:3">
+      <c r="A69" s="2">
+        <v>100200016</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" ht="17.25" spans="1:3">
+      <c r="A70" s="2">
+        <v>100200017</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" ht="17.25" spans="1:3">
+      <c r="A71" s="2">
+        <v>100200018</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" ht="17.25" spans="1:3">
+      <c r="A72" s="2">
+        <v>100200019</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" ht="17.25" spans="1:3">
+      <c r="A73" s="2">
+        <v>100200020</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="2">
+        <v>100300001</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="2">
+        <v>100300002</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="2">
+        <v>100300003</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="2">
+        <v>100300004</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="2">
+        <v>100300005</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="2">
+        <v>100300006</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="2">
+        <v>100300007</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="2">
+        <v>100300008</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="2">
+        <v>100300009</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="2">
+        <v>100300010</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" spans="1:4">
+      <c r="A84" s="2">
+        <v>100400001</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" s="4"/>
+    </row>
+    <row r="85" s="2" customFormat="1" spans="1:4">
+      <c r="A85" s="2">
+        <v>100400002</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" s="4"/>
+    </row>
+    <row r="86" s="2" customFormat="1" spans="1:4">
+      <c r="A86" s="2">
+        <v>100400003</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86" s="4"/>
+    </row>
+    <row r="87" s="2" customFormat="1" spans="1:4">
+      <c r="A87" s="2">
+        <v>100400004</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" s="4"/>
+    </row>
+    <row r="88" s="2" customFormat="1" spans="1:4">
+      <c r="A88" s="2">
+        <v>100400005</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" s="4"/>
+    </row>
+    <row r="89" s="2" customFormat="1" spans="1:4">
+      <c r="A89" s="2">
+        <v>100400006</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" s="4"/>
+    </row>
+    <row r="90" s="2" customFormat="1" spans="1:4">
+      <c r="A90" s="2">
+        <v>100400007</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" s="4"/>
+    </row>
+    <row r="91" s="2" customFormat="1" spans="1:4">
+      <c r="A91" s="2">
+        <v>100400008</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="4"/>
+    </row>
+    <row r="92" s="2" customFormat="1" spans="1:4">
+      <c r="A92" s="2">
+        <v>100400009</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" s="4"/>
+    </row>
+    <row r="93" s="2" customFormat="1" spans="1:4">
+      <c r="A93" s="2">
+        <v>100400010</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93" s="4"/>
+    </row>
+    <row r="94" s="2" customFormat="1" spans="1:4">
+      <c r="A94" s="2">
+        <v>100400011</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="4"/>
+    </row>
+    <row r="95" s="2" customFormat="1" spans="1:4">
+      <c r="A95" s="2">
+        <v>100400012</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95" s="4"/>
+    </row>
+    <row r="96" s="2" customFormat="1" spans="1:4">
+      <c r="A96" s="2">
+        <v>100400013</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" s="4"/>
+    </row>
+    <row r="97" s="2" customFormat="1" spans="1:4">
+      <c r="A97" s="2">
+        <v>100400014</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D97" s="4"/>
+    </row>
+    <row r="98" s="2" customFormat="1" spans="1:4">
+      <c r="A98" s="2">
+        <v>100400015</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D98" s="4"/>
+    </row>
+    <row r="99" s="2" customFormat="1" spans="1:4">
+      <c r="A99" s="2">
+        <v>100400016</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="4"/>
+    </row>
+    <row r="100" s="2" customFormat="1" spans="1:4">
+      <c r="A100" s="2">
+        <v>100400017</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D100" s="4"/>
+    </row>
+    <row r="101" s="2" customFormat="1" spans="1:4">
+      <c r="A101" s="2">
+        <v>100400018</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D101" s="4"/>
+    </row>
+    <row r="102" s="2" customFormat="1" spans="1:4">
+      <c r="A102" s="2">
+        <v>100400019</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" s="4"/>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="1:4">
+      <c r="A103" s="2">
+        <v>100400020</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D103" s="4"/>
+    </row>
+    <row r="104" s="2" customFormat="1" spans="1:4">
+      <c r="A104" s="2">
+        <v>100400021</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D104" s="4"/>
+    </row>
+    <row r="105" s="2" customFormat="1" spans="1:4">
+      <c r="A105" s="2">
+        <v>100400022</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D105" s="4"/>
+    </row>
+    <row r="106" s="2" customFormat="1" spans="1:4">
+      <c r="A106" s="2">
+        <v>100400023</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D106" s="4"/>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="1:4">
+      <c r="A107" s="2">
+        <v>100400024</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D107" s="4"/>
+    </row>
+    <row r="108" s="2" customFormat="1" spans="1:4">
+      <c r="A108" s="2">
+        <v>100400025</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D108" s="4"/>
+    </row>
+    <row r="109" s="2" customFormat="1" spans="1:4">
+      <c r="A109" s="2">
+        <v>100400026</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D109" s="4"/>
+    </row>
+    <row r="110" s="2" customFormat="1" spans="1:4">
+      <c r="A110" s="2">
+        <v>100400027</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D110" s="4"/>
+    </row>
+    <row r="111" s="2" customFormat="1" spans="1:4">
+      <c r="A111" s="2">
+        <v>100400028</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D111" s="4"/>
+    </row>
+    <row r="112" s="2" customFormat="1" spans="1:4">
+      <c r="A112" s="2">
+        <v>100400029</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D112" s="4"/>
+    </row>
+    <row r="113" s="2" customFormat="1" spans="1:4">
+      <c r="A113" s="2">
+        <v>100400030</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D113" s="4"/>
+    </row>
+    <row r="114" s="2" customFormat="1" spans="1:4">
+      <c r="A114" s="2">
+        <v>100400031</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D114" s="4"/>
+    </row>
+    <row r="115" s="2" customFormat="1" spans="1:4">
+      <c r="A115" s="2">
+        <v>100400032</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D115" s="4"/>
+    </row>
+    <row r="116" s="2" customFormat="1" spans="1:4">
+      <c r="A116" s="2">
+        <v>100400033</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D116" s="4"/>
+    </row>
+    <row r="117" s="2" customFormat="1" spans="1:4">
+      <c r="A117" s="2">
+        <v>100400034</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D117" s="4"/>
+    </row>
+    <row r="118" s="2" customFormat="1" spans="1:4">
+      <c r="A118" s="2">
+        <v>100400035</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D118" s="4"/>
+    </row>
+    <row r="119" s="2" customFormat="1" spans="1:4">
+      <c r="A119" s="2">
+        <v>100400036</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D119" s="4"/>
+    </row>
+    <row r="120" s="2" customFormat="1" spans="1:4">
+      <c r="A120" s="2">
+        <v>100400037</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D120" s="4"/>
+    </row>
+    <row r="121" s="2" customFormat="1" spans="1:4">
+      <c r="A121" s="2">
+        <v>100400038</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D121" s="4"/>
+    </row>
+    <row r="122" s="2" customFormat="1" spans="1:4">
+      <c r="A122" s="2">
+        <v>100400039</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D122" s="4"/>
+    </row>
+    <row r="123" s="2" customFormat="1" spans="1:4">
+      <c r="A123" s="2">
+        <v>100400040</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D123" s="4"/>
+    </row>
+    <row r="124" s="2" customFormat="1" spans="1:4">
+      <c r="A124" s="2">
+        <v>100400041</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D124" s="4"/>
+    </row>
+    <row r="125" s="2" customFormat="1" spans="1:4">
+      <c r="A125" s="2">
+        <v>100400042</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D125" s="4"/>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="2">
+        <v>100500001</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="2">
+        <v>100500002</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="2">
+        <v>100500003</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="2">
+        <v>100500004</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="2">
+        <v>100500005</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="2">
+        <v>100500006</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="2">
+        <v>100500007</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="2">
+        <v>100500008</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="2">
+        <v>100500009</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="2">
+        <v>100500010</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="2">
+        <v>100500011</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="2">
+        <v>100500012</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="2">
+        <v>100500013</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="2">
+        <v>100500014</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="2">
+        <v>100500015</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="2">
+        <v>100500016</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="2">
+        <v>100500017</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="2">
+        <v>100500018</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="2">
+        <v>100500019</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="2">
+        <v>100500020</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="2">
+        <v>100500021</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="2">
+        <v>100500022</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="2">
+        <v>100500023</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="2">
+        <v>200100001</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="2">
+        <v>200100002</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="2">
+        <v>200100003</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="2">
+        <v>200100004</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="2">
+        <v>200100005</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="2">
+        <v>200100006</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="2">
+        <v>200100007</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="2">
+        <v>200100008</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="2">
+        <v>200100009</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="2">
+        <v>200100010</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="2">
+        <v>200100011</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="2">
+        <v>200100012</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="2">
+        <v>200100013</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="2">
+        <v>200100014</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="2">
+        <v>200100015</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="2">
+        <v>200100016</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="2">
+        <v>200100017</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="2">
+        <v>200100018</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="2">
+        <v>200100019</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="2">
+        <v>200100020</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="2">
+        <v>200100021</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="2">
+        <v>200100022</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="2">
+        <v>200100023</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" s="2">
+        <v>200100024</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" s="2">
+        <v>200100025</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="2">
+        <v>200100026</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="2">
+        <v>200100027</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="2">
+        <v>200100028</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="2">
+        <v>200100029</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" s="2">
+        <v>200100030</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="2">
+        <v>200100031</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="2">
+        <v>200100032</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="2">
+        <v>200100033</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="2">
+        <v>200100034</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="2">
+        <v>200100035</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="2">
+        <v>200100036</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" s="2">
+        <v>200100037</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="186" s="2" customFormat="1" spans="1:4">
+      <c r="A186" s="2">
+        <v>200101001</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D186" s="4"/>
+    </row>
+    <row r="187" s="2" customFormat="1" spans="1:4">
+      <c r="A187" s="2">
+        <v>200101002</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D187" s="4"/>
+    </row>
+    <row r="188" s="2" customFormat="1" spans="1:4">
+      <c r="A188" s="2">
+        <v>200101003</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D188" s="4"/>
+    </row>
+    <row r="189" s="2" customFormat="1" spans="1:4">
+      <c r="A189" s="2">
+        <v>200101004</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D189" s="4"/>
+    </row>
+    <row r="190" s="2" customFormat="1" spans="1:4">
+      <c r="A190" s="2">
+        <v>200101005</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D190" s="4"/>
+    </row>
+    <row r="191" s="2" customFormat="1" spans="1:4">
+      <c r="A191" s="2">
+        <v>200101006</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D191" s="4"/>
+    </row>
+    <row r="192" s="2" customFormat="1" spans="1:4">
+      <c r="A192" s="2">
+        <v>200101007</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D192" s="4"/>
+    </row>
+    <row r="193" s="2" customFormat="1" spans="1:4">
+      <c r="A193" s="2">
+        <v>200101008</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D193" s="4"/>
+    </row>
+    <row r="194" s="2" customFormat="1" spans="1:4">
+      <c r="A194" s="2">
+        <v>200101009</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D194" s="4"/>
+    </row>
+    <row r="195" s="2" customFormat="1" spans="1:4">
+      <c r="A195" s="2">
+        <v>200101010</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D195" s="4"/>
+    </row>
+    <row r="196" s="2" customFormat="1" spans="1:4">
+      <c r="A196" s="2">
+        <v>200101011</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D196" s="4"/>
+    </row>
+    <row r="197" s="2" customFormat="1" spans="1:4">
+      <c r="A197" s="2">
+        <v>200101012</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D197" s="4"/>
+    </row>
+    <row r="198" s="2" customFormat="1" spans="1:4">
+      <c r="A198" s="2">
+        <v>200101013</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D198" s="4"/>
+    </row>
+    <row r="199" s="2" customFormat="1" spans="1:4">
+      <c r="A199" s="2">
+        <v>200101014</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D199" s="4"/>
+    </row>
+    <row r="200" s="2" customFormat="1" spans="1:4">
+      <c r="A200" s="2">
+        <v>200101015</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D200" s="4"/>
+    </row>
+    <row r="201" s="2" customFormat="1" spans="1:4">
+      <c r="A201" s="2">
+        <v>200101016</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D201" s="4"/>
+    </row>
+    <row r="202" s="2" customFormat="1" spans="1:4">
+      <c r="A202" s="2">
+        <v>200101017</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D202" s="4"/>
+    </row>
+    <row r="203" s="2" customFormat="1" spans="1:4">
+      <c r="A203" s="2">
+        <v>200101018</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D203" s="4"/>
+    </row>
+    <row r="204" s="2" customFormat="1" spans="1:4">
+      <c r="A204" s="2">
+        <v>200101019</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D204" s="4"/>
+    </row>
+    <row r="205" s="2" customFormat="1" spans="1:4">
+      <c r="A205" s="2">
+        <v>200101020</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D205" s="4"/>
+    </row>
+    <row r="206" s="2" customFormat="1" spans="1:4">
+      <c r="A206" s="2">
+        <v>200101021</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D206" s="4"/>
+    </row>
+    <row r="207" s="2" customFormat="1" spans="1:4">
+      <c r="A207" s="2">
+        <v>200101022</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D207" s="4"/>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="2">
+        <v>200300001</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="209" ht="17.25" spans="1:3">
+      <c r="A209" s="2">
+        <v>200300002</v>
+      </c>
+      <c r="B209" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="210" ht="51.75" spans="1:3">
+      <c r="A210" s="2">
+        <v>200300003</v>
+      </c>
+      <c r="B210" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="211" ht="34.5" spans="1:3">
+      <c r="A211" s="2">
+        <v>200300004</v>
+      </c>
+      <c r="B211" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="212" ht="34.5" spans="1:3">
+      <c r="A212" s="2">
+        <v>200300005</v>
+      </c>
+      <c r="B212" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="213" ht="17.25" spans="1:3">
+      <c r="A213" s="2">
+        <v>200300006</v>
+      </c>
+      <c r="B213" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="214" ht="34.5" spans="1:3">
+      <c r="A214" s="2">
+        <v>200300007</v>
+      </c>
+      <c r="B214" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="215" ht="17.25" spans="1:3">
+      <c r="A215" s="2">
+        <v>200300008</v>
+      </c>
+      <c r="B215" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="216" ht="34.5" spans="1:3">
+      <c r="A216" s="2">
+        <v>200300009</v>
+      </c>
+      <c r="B216" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="217" ht="17.25" spans="1:3">
+      <c r="A217" s="2">
+        <v>200300010</v>
+      </c>
+      <c r="B217" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>200400001</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D218" s="2"/>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>200400002</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D219" s="2"/>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>200400003</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D220" s="2"/>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>200400004</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D221" s="2"/>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>200400005</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D222" s="2"/>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>200400006</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D223" s="2"/>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>200400007</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D224" s="2"/>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>200400008</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D225" s="2"/>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="2">
+        <v>200500001</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" s="2">
+        <v>200500002</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" s="2">
+        <v>200500003</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" s="2">
+        <v>200500004</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" s="2">
+        <v>200500005</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" s="2">
+        <v>200500006</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" s="2">
+        <v>200500007</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" s="2">
+        <v>200500008</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" s="2">
+        <v>200500009</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" s="2">
+        <v>200500010</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" s="2">
+        <v>200500011</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" s="2">
+        <v>200500012</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" s="2">
+        <v>200500013</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" s="2">
+        <v>200500014</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" s="2">
+        <v>200500015</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" s="2">
+        <v>200500016</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" s="2">
+        <v>200500017</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" s="2">
+        <v>200500018</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="2">
+        <v>200500019</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="2">
+        <v>200500020</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="2">
+        <v>200500021</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="2">
+        <v>200500022</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="2">
+        <v>200500023</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="2">
+        <v>200500024</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -1956,27 +5438,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.125" style="5" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1984,13 +5466,13 @@
       <c r="A2" s="2">
         <v>10001</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1998,13 +5480,13 @@
       <c r="A3" s="2">
         <v>10002</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2012,13 +5494,13 @@
       <c r="A4" s="2">
         <v>10003</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2026,13 +5508,13 @@
       <c r="A5" s="2">
         <v>10004</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2040,13 +5522,13 @@
       <c r="A6" s="2">
         <v>10005</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2054,13 +5536,13 @@
       <c r="A7" s="2">
         <v>10006</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2068,13 +5550,13 @@
       <c r="A8" s="2">
         <v>10007</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2082,13 +5564,13 @@
       <c r="A9" s="2">
         <v>10008</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2096,13 +5578,13 @@
       <c r="A10" s="2">
         <v>10009</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2110,13 +5592,13 @@
       <c r="A11" s="2">
         <v>10010</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2124,13 +5606,13 @@
       <c r="A12" s="2">
         <v>10011</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2138,13 +5620,13 @@
       <c r="A13" s="2">
         <v>10012</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2152,13 +5634,13 @@
       <c r="A14" s="2">
         <v>10013</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2166,13 +5648,13 @@
       <c r="A15" s="2">
         <v>10014</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2180,13 +5662,13 @@
       <c r="A16" s="2">
         <v>10015</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2194,13 +5676,13 @@
       <c r="A17" s="2">
         <v>10016</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2208,13 +5690,13 @@
       <c r="A18" s="2">
         <v>10017</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2222,13 +5704,13 @@
       <c r="A19" s="2">
         <v>10018</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2236,13 +5718,13 @@
       <c r="A20" s="2">
         <v>10019</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2250,13 +5732,13 @@
       <c r="A21" s="2">
         <v>10020</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2264,13 +5746,13 @@
       <c r="A22" s="2">
         <v>10021</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2278,13 +5760,13 @@
       <c r="A23" s="2">
         <v>10022</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2292,13 +5774,13 @@
       <c r="A24" s="2">
         <v>10023</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2306,7 +5788,7 @@
       <c r="A25" s="2">
         <v>11000</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2314,7 +5796,7 @@
       <c r="A26" s="2">
         <v>12000</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2322,7 +5804,7 @@
       <c r="A27" s="2">
         <v>13000</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2330,7 +5812,7 @@
       <c r="A28" s="2">
         <v>14000</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2338,13 +5820,13 @@
       <c r="A29" s="2">
         <v>100100001</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2352,13 +5834,13 @@
       <c r="A30" s="2">
         <v>100100002</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B30" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2366,13 +5848,13 @@
       <c r="A31" s="2">
         <v>100100003</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="B31" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2380,27 +5862,27 @@
       <c r="A32" s="2">
         <v>100100004</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B32" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>82</v>
+      <c r="D32" s="5" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
         <v>100100005</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2408,13 +5890,13 @@
       <c r="A34" s="2">
         <v>100100006</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B34" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2422,13 +5904,13 @@
       <c r="A35" s="2">
         <v>100100007</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B35" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2436,13 +5918,13 @@
       <c r="A36" s="2">
         <v>100100008</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="B36" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2450,13 +5932,13 @@
       <c r="A37" s="2">
         <v>100100009</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="B37" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2464,13 +5946,13 @@
       <c r="A38" s="2">
         <v>100100010</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="B38" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2478,13 +5960,13 @@
       <c r="A39" s="2">
         <v>100100011</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="B39" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2492,13 +5974,13 @@
       <c r="A40" s="2">
         <v>100100012</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="B40" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2506,13 +5988,13 @@
       <c r="A41" s="2">
         <v>100100013</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="B41" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2520,13 +6002,13 @@
       <c r="A42" s="2">
         <v>100100014</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="B42" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2534,13 +6016,13 @@
       <c r="A43" s="2">
         <v>100100015</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B43" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2548,13 +6030,13 @@
       <c r="A44" s="2">
         <v>100100016</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B44" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2562,13 +6044,13 @@
       <c r="A45" s="2">
         <v>100100017</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B45" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2576,13 +6058,13 @@
       <c r="A46" s="2">
         <v>100100018</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="B46" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2590,13 +6072,13 @@
       <c r="A47" s="2">
         <v>100100019</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B47" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="5" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2604,13 +6086,13 @@
       <c r="A48" s="2">
         <v>100100020</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="B48" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2618,13 +6100,13 @@
       <c r="A49" s="2">
         <v>100100021</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="B49" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2632,13 +6114,13 @@
       <c r="A50" s="2">
         <v>100100022</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="B50" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2646,13 +6128,13 @@
       <c r="A51" s="2">
         <v>100100023</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="B51" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="5" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2660,22 +6142,2772 @@
       <c r="A52" s="2">
         <v>100100024</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2">
+        <v>100100025</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2">
+        <v>100200001</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" ht="17.25" spans="1:4">
+      <c r="A55" s="2">
+        <v>100200002</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" ht="17.25" spans="1:4">
+      <c r="A56" s="2">
+        <v>100200003</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" ht="17.25" spans="1:4">
+      <c r="A57" s="2">
+        <v>100200004</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" ht="17.25" spans="1:4">
+      <c r="A58" s="2">
+        <v>100200005</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" spans="1:4">
+      <c r="A59" s="2">
+        <v>100200006</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" spans="1:4">
+      <c r="A60" s="2">
+        <v>100200007</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" spans="1:4">
+      <c r="A61" s="2">
+        <v>100200008</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" ht="17.25" spans="1:4">
+      <c r="A62" s="2">
+        <v>100200009</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" ht="17.25" spans="1:4">
+      <c r="A63" s="2">
+        <v>100200010</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" spans="1:4">
+      <c r="A64" s="2">
+        <v>100200011</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" ht="17.25" spans="1:4">
+      <c r="A65" s="2">
+        <v>100200012</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" ht="17.25" spans="1:4">
+      <c r="A66" s="2">
+        <v>100200013</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" ht="17.25" spans="1:4">
+      <c r="A67" s="2">
+        <v>100200014</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" ht="17.25" spans="1:4">
+      <c r="A68" s="2">
+        <v>100200015</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" ht="17.25" spans="1:4">
+      <c r="A69" s="2">
+        <v>100200016</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" ht="17.25" spans="1:4">
+      <c r="A70" s="2">
+        <v>100200017</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" ht="17.25" spans="1:4">
+      <c r="A71" s="2">
+        <v>100200018</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" ht="17.25" spans="1:4">
+      <c r="A72" s="2">
+        <v>100200019</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" ht="17.25" spans="1:4">
+      <c r="A73" s="2">
+        <v>100200020</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="2">
+        <v>100300001</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="2">
+        <v>100300002</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="2">
+        <v>100300003</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="2">
+        <v>100300004</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="2">
+        <v>100300005</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="2">
+        <v>100300006</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="2">
+        <v>100300007</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="2">
+        <v>100300008</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="2">
+        <v>100300009</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="2">
+        <v>100300010</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A84" s="2">
+        <v>100400001</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A85" s="2">
+        <v>100400002</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A86" s="2">
+        <v>100400003</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A87" s="2">
+        <v>100400004</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A88" s="2">
+        <v>100400005</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A89" s="2">
+        <v>100400006</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A90" s="2">
+        <v>100400007</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A91" s="2">
+        <v>100400008</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A92" s="2">
+        <v>100400009</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A93" s="2">
+        <v>100400010</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A94" s="2">
+        <v>100400011</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A95" s="2">
+        <v>100400012</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A96" s="2">
+        <v>100400013</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A97" s="2">
+        <v>100400014</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A98" s="2">
+        <v>100400015</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A99" s="2">
+        <v>100400016</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A100" s="2">
+        <v>100400017</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A101" s="2">
+        <v>100400018</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A102" s="2">
+        <v>100400019</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A103" s="2">
+        <v>100400020</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A104" s="2">
+        <v>100400021</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D104" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2">
-        <v>100200001</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>54</v>
+    </row>
+    <row r="105" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A105" s="2">
+        <v>100400022</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A106" s="2">
+        <v>100400023</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A107" s="2">
+        <v>100400024</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A108" s="2">
+        <v>100400025</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A109" s="2">
+        <v>100400026</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A110" s="2">
+        <v>100400027</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="111" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A111" s="2">
+        <v>100400028</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="112" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A112" s="2">
+        <v>100400029</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A113" s="2">
+        <v>100400030</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A114" s="2">
+        <v>100400031</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="115" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A115" s="2">
+        <v>100400032</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A116" s="2">
+        <v>100400033</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A117" s="2">
+        <v>100400034</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="118" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A118" s="2">
+        <v>100400035</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A119" s="2">
+        <v>100400036</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="120" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A120" s="2">
+        <v>100400037</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="121" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A121" s="2">
+        <v>100400038</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A122" s="2">
+        <v>100400039</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="123" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A123" s="2">
+        <v>100400040</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="124" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A124" s="2">
+        <v>100400041</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="125" s="2" customFormat="1" ht="17.25" spans="1:4">
+      <c r="A125" s="2">
+        <v>100400042</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="2">
+        <v>100500001</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="2">
+        <v>100500002</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="2">
+        <v>100500003</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="2">
+        <v>100500004</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="2">
+        <v>100500005</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="2">
+        <v>100500006</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="2">
+        <v>100500007</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="2">
+        <v>100500008</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="2">
+        <v>100500009</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="2">
+        <v>100500010</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="2">
+        <v>100500011</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="2">
+        <v>100500012</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="2">
+        <v>100500013</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="2">
+        <v>100500014</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="2">
+        <v>100500015</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="2">
+        <v>100500016</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="2">
+        <v>100500017</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="2">
+        <v>100500018</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="2">
+        <v>100500019</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="2">
+        <v>100500020</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="2">
+        <v>100500021</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="2">
+        <v>100500022</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="2">
+        <v>100500023</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="149" s="2" customFormat="1" spans="1:4">
+      <c r="A149" s="2">
+        <v>200100001</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="150" s="2" customFormat="1" spans="1:4">
+      <c r="A150" s="2">
+        <v>200100002</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="151" s="2" customFormat="1" spans="1:4">
+      <c r="A151" s="2">
+        <v>200100003</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="152" s="2" customFormat="1" spans="1:4">
+      <c r="A152" s="2">
+        <v>200100004</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="153" s="2" customFormat="1" spans="1:4">
+      <c r="A153" s="2">
+        <v>200100005</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="154" s="2" customFormat="1" spans="1:4">
+      <c r="A154" s="2">
+        <v>200100006</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="155" s="2" customFormat="1" spans="1:4">
+      <c r="A155" s="2">
+        <v>200100007</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="156" s="2" customFormat="1" spans="1:4">
+      <c r="A156" s="2">
+        <v>200100008</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="157" s="2" customFormat="1" spans="1:4">
+      <c r="A157" s="2">
+        <v>200100009</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="158" s="2" customFormat="1" spans="1:4">
+      <c r="A158" s="2">
+        <v>200100010</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="159" s="2" customFormat="1" spans="1:4">
+      <c r="A159" s="2">
+        <v>200100011</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="160" s="2" customFormat="1" spans="1:4">
+      <c r="A160" s="2">
+        <v>200100012</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="161" s="2" customFormat="1" spans="1:4">
+      <c r="A161" s="2">
+        <v>200100013</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" s="2" customFormat="1" spans="1:4">
+      <c r="A162" s="2">
+        <v>200100014</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" s="2" customFormat="1" spans="1:4">
+      <c r="A163" s="2">
+        <v>200100015</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164" s="2" customFormat="1" spans="1:4">
+      <c r="A164" s="2">
+        <v>200100016</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="165" s="2" customFormat="1" spans="1:4">
+      <c r="A165" s="2">
+        <v>200100017</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="166" s="2" customFormat="1" spans="1:4">
+      <c r="A166" s="2">
+        <v>200100018</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" s="2" customFormat="1" spans="1:4">
+      <c r="A167" s="2">
+        <v>200100019</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="168" s="2" customFormat="1" spans="1:4">
+      <c r="A168" s="2">
+        <v>200100020</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="169" s="2" customFormat="1" spans="1:4">
+      <c r="A169" s="2">
+        <v>200100021</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170" s="2" customFormat="1" spans="1:4">
+      <c r="A170" s="2">
+        <v>200100022</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" s="2" customFormat="1" spans="1:4">
+      <c r="A171" s="2">
+        <v>200100023</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="172" s="2" customFormat="1" spans="1:4">
+      <c r="A172" s="2">
+        <v>200100024</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="173" s="2" customFormat="1" spans="1:4">
+      <c r="A173" s="2">
+        <v>200100025</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="174" s="2" customFormat="1" spans="1:4">
+      <c r="A174" s="2">
+        <v>200100026</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="175" s="2" customFormat="1" spans="1:4">
+      <c r="A175" s="2">
+        <v>200100027</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="176" s="2" customFormat="1" spans="1:4">
+      <c r="A176" s="2">
+        <v>200100028</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" s="2" customFormat="1" spans="1:4">
+      <c r="A177" s="2">
+        <v>200100029</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="178" s="2" customFormat="1" spans="1:4">
+      <c r="A178" s="2">
+        <v>200100030</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" s="2" customFormat="1" spans="1:4">
+      <c r="A179" s="2">
+        <v>200100031</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="180" s="2" customFormat="1" spans="1:4">
+      <c r="A180" s="2">
+        <v>200100032</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="181" s="2" customFormat="1" spans="1:4">
+      <c r="A181" s="2">
+        <v>200100033</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="182" s="2" customFormat="1" spans="1:4">
+      <c r="A182" s="2">
+        <v>200100034</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="183" s="2" customFormat="1" spans="1:4">
+      <c r="A183" s="2">
+        <v>200100035</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="184" s="2" customFormat="1" spans="1:4">
+      <c r="A184" s="2">
+        <v>200100036</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="185" s="2" customFormat="1" spans="1:4">
+      <c r="A185" s="2">
+        <v>200100037</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="186" s="2" customFormat="1" spans="1:4">
+      <c r="A186" s="2">
+        <v>200101001</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="187" s="2" customFormat="1" spans="1:4">
+      <c r="A187" s="2">
+        <v>200101002</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="188" s="2" customFormat="1" spans="1:4">
+      <c r="A188" s="2">
+        <v>200101003</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="189" s="2" customFormat="1" spans="1:4">
+      <c r="A189" s="2">
+        <v>200101004</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D189" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="190" s="2" customFormat="1" spans="1:4">
+      <c r="A190" s="2">
+        <v>200101005</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="191" s="2" customFormat="1" spans="1:4">
+      <c r="A191" s="2">
+        <v>200101006</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="192" s="2" customFormat="1" spans="1:4">
+      <c r="A192" s="2">
+        <v>200101007</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="193" s="2" customFormat="1" spans="1:4">
+      <c r="A193" s="2">
+        <v>200101008</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="194" s="2" customFormat="1" spans="1:4">
+      <c r="A194" s="2">
+        <v>200101009</v>
+      </c>
+      <c r="B194" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="195" s="2" customFormat="1" spans="1:4">
+      <c r="A195" s="2">
+        <v>200101010</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="196" s="2" customFormat="1" spans="1:4">
+      <c r="A196" s="2">
+        <v>200101011</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="197" s="2" customFormat="1" spans="1:4">
+      <c r="A197" s="2">
+        <v>200101012</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D197" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="198" s="2" customFormat="1" spans="1:4">
+      <c r="A198" s="2">
+        <v>200101013</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="199" s="2" customFormat="1" spans="1:4">
+      <c r="A199" s="2">
+        <v>200101014</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D199" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="200" s="2" customFormat="1" spans="1:4">
+      <c r="A200" s="2">
+        <v>200101015</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D200" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="201" s="2" customFormat="1" spans="1:4">
+      <c r="A201" s="2">
+        <v>200101016</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="202" s="2" customFormat="1" spans="1:4">
+      <c r="A202" s="2">
+        <v>200101017</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D202" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="203" s="2" customFormat="1" spans="1:4">
+      <c r="A203" s="2">
+        <v>200101018</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D203" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="204" s="2" customFormat="1" spans="1:4">
+      <c r="A204" s="2">
+        <v>200101019</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D204" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="205" s="2" customFormat="1" spans="1:4">
+      <c r="A205" s="2">
+        <v>200101020</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D205" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="206" s="2" customFormat="1" spans="1:4">
+      <c r="A206" s="2">
+        <v>200101021</v>
+      </c>
+      <c r="B206" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D206" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="207" s="2" customFormat="1" spans="1:4">
+      <c r="A207" s="2">
+        <v>200101022</v>
+      </c>
+      <c r="B207" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D207" s="15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>200400001</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>200400002</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>200400003</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>200400004</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>200400005</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>200400006</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>200400007</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>200400008</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>200300001</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="217" ht="17.25" spans="1:4">
+      <c r="A217" s="2">
+        <v>200300002</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D217" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="218" ht="103.5" spans="1:4">
+      <c r="A218" s="2">
+        <v>200300003</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D218" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="219" ht="69" spans="1:4">
+      <c r="A219" s="2">
+        <v>200300004</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D219" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="220" ht="69" spans="1:4">
+      <c r="A220" s="2">
+        <v>200300005</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D220" s="16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="221" ht="34.5" spans="1:4">
+      <c r="A221" s="2">
+        <v>200300006</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D221" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="222" ht="69" spans="1:4">
+      <c r="A222" s="2">
+        <v>200300007</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D222" s="16" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="223" ht="34.5" spans="1:4">
+      <c r="A223" s="2">
+        <v>200300008</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D223" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="224" ht="51.75" spans="1:4">
+      <c r="A224" s="2">
+        <v>200300009</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D224" s="16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="225" ht="34.5" spans="1:4">
+      <c r="A225" s="2">
+        <v>200300010</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D225" s="16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>200500001</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>200500002</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>200500003</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>200500004</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>200500005</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>200500006</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>200500007</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>200500008</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>200500009</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>200500010</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>200500011</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>200500012</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>200500013</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>200500014</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>200500015</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>200500016</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>200500017</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>200500018</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>200500019</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>200500020</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>200500021</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>200500022</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>200500023</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>200500024</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
